--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>117834123</v>
       </c>
       <c r="B5" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,6 +1299,126 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120272749</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jonasbosjön, vägen, Eret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571688</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6694405</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1304,7 +1304,7 @@
         <v>120272749</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1424,7 +1424,7 @@
         <v>120815934</v>
       </c>
       <c r="B8" t="n">
-        <v>57501</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>121197106</v>
       </c>
       <c r="B9" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>121197106</v>
       </c>
       <c r="B9" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>121197106</v>
       </c>
       <c r="B9" t="n">
-        <v>100360</v>
+        <v>100361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>121197106</v>
       </c>
       <c r="B9" t="n">
-        <v>100361</v>
+        <v>100364</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,7 +1544,7 @@
         <v>121197106</v>
       </c>
       <c r="B9" t="n">
-        <v>100364</v>
+        <v>100370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1663,6 +1663,250 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121569427</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57508</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Granskogen norr linjen, Eret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>570915</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6694101</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121557904</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57508</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Granskogen n linjen, Eret, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>570918</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6694097</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elisabeth Norman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1544,7 +1544,7 @@
         <v>121197106</v>
       </c>
       <c r="B9" t="n">
-        <v>100370</v>
+        <v>100371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>121569427</v>
       </c>
       <c r="B10" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>121557904</v>
       </c>
       <c r="B11" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569427</v>
+        <v>121557904</v>
       </c>
       <c r="B10" t="n">
         <v>57509</v>
@@ -1699,28 +1699,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskogen norr linjen, Eret, Dlr</t>
+          <t>Granskogen n linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570915</v>
+        <v>570918</v>
       </c>
       <c r="R10" t="n">
-        <v>6694101</v>
+        <v>6694097</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,22 +1748,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,7 +1790,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121557904</v>
+        <v>121569427</v>
       </c>
       <c r="B11" t="n">
         <v>57509</v>
@@ -1819,32 +1823,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granskogen n linjen, Eret, Dlr</t>
+          <t>Granskogen norr linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570918</v>
+        <v>570915</v>
       </c>
       <c r="R11" t="n">
-        <v>6694097</v>
+        <v>6694101</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121557904</v>
+        <v>121569427</v>
       </c>
       <c r="B10" t="n">
         <v>57509</v>
@@ -1699,32 +1699,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskogen n linjen, Eret, Dlr</t>
+          <t>Granskogen norr linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570918</v>
+        <v>570915</v>
       </c>
       <c r="R10" t="n">
-        <v>6694097</v>
+        <v>6694101</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,22 +1744,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,7 +1786,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569427</v>
+        <v>121557904</v>
       </c>
       <c r="B11" t="n">
         <v>57509</v>
@@ -1823,28 +1819,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granskogen norr linjen, Eret, Dlr</t>
+          <t>Granskogen n linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570915</v>
+        <v>570918</v>
       </c>
       <c r="R11" t="n">
-        <v>6694101</v>
+        <v>6694097</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1669,7 +1669,7 @@
         <v>121569427</v>
       </c>
       <c r="B10" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>121557904</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569427</v>
+        <v>121557904</v>
       </c>
       <c r="B10" t="n">
         <v>57510</v>
@@ -1699,28 +1699,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskogen norr linjen, Eret, Dlr</t>
+          <t>Granskogen n linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570915</v>
+        <v>570918</v>
       </c>
       <c r="R10" t="n">
-        <v>6694101</v>
+        <v>6694097</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,22 +1748,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,7 +1790,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121557904</v>
+        <v>121569427</v>
       </c>
       <c r="B11" t="n">
         <v>57510</v>
@@ -1819,32 +1823,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granskogen n linjen, Eret, Dlr</t>
+          <t>Granskogen norr linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570918</v>
+        <v>570915</v>
       </c>
       <c r="R11" t="n">
-        <v>6694097</v>
+        <v>6694101</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1666,7 +1666,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121557904</v>
+        <v>121569427</v>
       </c>
       <c r="B10" t="n">
         <v>57510</v>
@@ -1699,32 +1699,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskogen n linjen, Eret, Dlr</t>
+          <t>Granskogen norr linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570918</v>
+        <v>570915</v>
       </c>
       <c r="R10" t="n">
-        <v>6694097</v>
+        <v>6694101</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,22 +1744,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,7 +1786,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569427</v>
+        <v>121557904</v>
       </c>
       <c r="B11" t="n">
         <v>57510</v>
@@ -1823,28 +1819,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granskogen norr linjen, Eret, Dlr</t>
+          <t>Granskogen n linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570915</v>
+        <v>570918</v>
       </c>
       <c r="R11" t="n">
-        <v>6694101</v>
+        <v>6694097</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -1666,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569427</v>
+        <v>121557904</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,28 +1699,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskogen norr linjen, Eret, Dlr</t>
+          <t>Granskogen n linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570915</v>
+        <v>570918</v>
       </c>
       <c r="R10" t="n">
-        <v>6694101</v>
+        <v>6694097</v>
       </c>
       <c r="S10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1744,22 +1748,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1786,10 +1790,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121557904</v>
+        <v>121569427</v>
       </c>
       <c r="B11" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1819,32 +1823,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granskogen n linjen, Eret, Dlr</t>
+          <t>Granskogen norr linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570918</v>
+        <v>570915</v>
       </c>
       <c r="R11" t="n">
-        <v>6694097</v>
+        <v>6694101</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1868,22 +1868,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 46595-2023 artfynd.xlsx
+++ b/artfynd/A 46595-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,10 +1541,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121197106</v>
+        <v>121557904</v>
       </c>
       <c r="B9" t="n">
-        <v>100371</v>
+        <v>57518</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1553,25 +1553,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1579,27 +1579,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Jonasbosjön, vägen, Eret, Dlr</t>
+          <t>Granskogen n linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571688</v>
+        <v>570918</v>
       </c>
       <c r="R9" t="n">
-        <v>6694405</v>
+        <v>6694097</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1623,22 +1623,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,7 +1647,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1666,7 +1665,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121557904</v>
+        <v>121569427</v>
       </c>
       <c r="B10" t="n">
         <v>57518</v>
@@ -1699,32 +1698,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskogen n linjen, Eret, Dlr</t>
+          <t>Granskogen norr linjen, Eret, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570918</v>
+        <v>570915</v>
       </c>
       <c r="R10" t="n">
-        <v>6694097</v>
+        <v>6694101</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1748,22 +1743,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1787,126 +1782,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>121569427</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Granskogen norr linjen, Eret, Dlr</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>570915</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6694101</v>
-      </c>
-      <c r="S11" t="n">
-        <v>75</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Hedemora</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Husby</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Elisabeth Norman</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Elisabeth Norman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
